--- a/health-register/screenshots/exports/semester.xlsx
+++ b/health-register/screenshots/exports/semester.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -452,7 +452,7 @@
         <v>عدد الطلاب</v>
       </c>
       <c r="B8" t="str">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9">
@@ -468,7 +468,7 @@
         <v>حالات نشطة: سكري</v>
       </c>
       <c r="B10" t="str">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -524,7 +524,7 @@
         <v>نسبة الطلبة المستفيدين من البرامج</v>
       </c>
       <c r="B17" t="str">
-        <v>38.9%</v>
+        <v>37.8%</v>
       </c>
     </row>
     <row r="19">
@@ -559,10 +559,10 @@
         <v>لم يُنفذ</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="str">
-        <v>7%</v>
+        <v>13%</v>
       </c>
     </row>
     <row r="23">
@@ -592,10 +592,10 @@
         <v>متأخر التحديث</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="str">
-        <v>7%</v>
+        <v>0%</v>
       </c>
     </row>
     <row r="27">
@@ -686,7 +686,7 @@
         <v>3</v>
       </c>
       <c r="B31" t="str">
-        <v>تفقد البيئة المدرسية والمقصف (الفصل الأول)</v>
+        <v>الرسائل التثقيفية لأولياء الأمور (الفصل الأول)</v>
       </c>
       <c r="C31" t="str">
         <v>الفصل الأول</v>
@@ -738,7 +738,7 @@
         <v>5</v>
       </c>
       <c r="B33" t="str">
-        <v>التوعية بالحساسية</v>
+        <v>الفحص الاستكشافي (الفصل الأول)</v>
       </c>
       <c r="C33" t="str">
         <v>الفصل الأول</v>
@@ -764,7 +764,7 @@
         <v>6</v>
       </c>
       <c r="B34" t="str">
-        <v>التعامل مع الحالات الصحية</v>
+        <v>اللقاء التعريفي لبرامج الصحة المدرسية</v>
       </c>
       <c r="C34" t="str">
         <v>الفصل الأول</v>
@@ -773,13 +773,13 @@
         <v>10‏/3‏/1448هـ — 23‏/8‏/2026م</v>
       </c>
       <c r="E34" t="str">
-        <v>مخطط</v>
+        <v>منفذ</v>
       </c>
       <c r="F34" t="str">
-        <v>—</v>
-      </c>
-      <c r="G34" t="str">
-        <v>—</v>
+        <v>17‏/3‏/1448هـ — 30‏/8‏/2026م</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
       </c>
       <c r="H34" t="str">
         <v>—</v>
@@ -816,7 +816,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="str">
-        <v>الرسائل التثقيفية لأولياء الأمور (الفصل الأول)</v>
+        <v>التوعية بالحساسية</v>
       </c>
       <c r="C36" t="str">
         <v>الفصل الأول</v>
@@ -842,7 +842,7 @@
         <v>9</v>
       </c>
       <c r="B37" t="str">
-        <v>اللقاء التعريفي لبرامج الصحة المدرسية</v>
+        <v>التعامل مع الحالات الصحية</v>
       </c>
       <c r="C37" t="str">
         <v>الفصل الأول</v>
@@ -851,13 +851,13 @@
         <v>10‏/3‏/1448هـ — 23‏/8‏/2026م</v>
       </c>
       <c r="E37" t="str">
-        <v>منفذ</v>
+        <v>مخطط</v>
       </c>
       <c r="F37" t="str">
-        <v>17‏/3‏/1448هـ — 30‏/8‏/2026م</v>
-      </c>
-      <c r="G37">
-        <v>4</v>
+        <v>—</v>
+      </c>
+      <c r="G37" t="str">
+        <v>—</v>
       </c>
       <c r="H37" t="str">
         <v>—</v>
@@ -894,7 +894,7 @@
         <v>11</v>
       </c>
       <c r="B39" t="str">
-        <v>الفحص الاستكشافي (الفصل الأول)</v>
+        <v>تفقد البيئة المدرسية والمقصف (الفصل الأول)</v>
       </c>
       <c r="C39" t="str">
         <v>الفصل الأول</v>
@@ -929,7 +929,7 @@
         <v>25‏/3‏/1448هـ — 7‏/9‏/2026م</v>
       </c>
       <c r="E40" t="str">
-        <v>متأخر التحديث</v>
+        <v>لم يُنفذ</v>
       </c>
       <c r="F40" t="str">
         <v>—</v>
@@ -938,7 +938,7 @@
         <v>—</v>
       </c>
       <c r="H40" t="str">
-        <v>—</v>
+        <v>ظروف جوية</v>
       </c>
     </row>
     <row r="41">
@@ -1034,36 +1034,36 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
+        <v>ظروف جوية</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
         <v>تعارض مع الاختبارات</v>
       </c>
-      <c r="B47">
+      <c r="B48">
         <v>2</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>سجلات المتابعة الرسمية خلال الفصل</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>السجل</v>
-      </c>
-      <c r="B50" t="str">
-        <v>عدد الحالات</v>
+        <v>سجلات المتابعة الرسمية خلال الفصل</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>الأمراض المعدية</v>
-      </c>
-      <c r="B51">
-        <v>1</v>
+        <v>السجل</v>
+      </c>
+      <c r="B51" t="str">
+        <v>عدد الحالات</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>الأمراض المزمنة</v>
+        <v>الأمراض المعدية</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -1071,44 +1071,44 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
+        <v>الأمراض المزمنة</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
         <v>الحالات الطارئة</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>زيارات العيادة</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>النتيجة</v>
-      </c>
-      <c r="B56" t="str">
-        <v>العدد</v>
+        <v>زيارات العيادة</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>عاد للفصل</v>
-      </c>
-      <c r="B57">
-        <v>2</v>
+        <v>النتيجة</v>
+      </c>
+      <c r="B57" t="str">
+        <v>العدد</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>أُرسل للمنزل</v>
+        <v>عاد للفصل</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>حُوّل</v>
+        <v>أُرسل للمنزل</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -1116,36 +1116,36 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
+        <v>حُوّل</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
         <v>الإجمالي</v>
       </c>
-      <c r="B60">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>التحويل للمراكز الصحية</v>
+      <c r="B61">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>الحالة</v>
-      </c>
-      <c r="B63" t="str">
-        <v>العدد</v>
+        <v>التحويل للمراكز الصحية</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>مرسل</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>الحالة</v>
+      </c>
+      <c r="B64" t="str">
+        <v>العدد</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>تمت المراجعة</v>
+        <v>مرسل</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -1153,94 +1153,102 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>مغلق</v>
+        <v>تمت المراجعة</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
+        <v>مغلق</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
         <v>الإجمالي</v>
       </c>
-      <c r="B67">
+      <c r="B68">
         <v>2</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>تفقد البيئة المدرسية (9‏/4‏/1448هـ — 20‏/9‏/2026م)</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>القسم</v>
-      </c>
-      <c r="B70" t="str">
-        <v>نعم/المجاب</v>
-      </c>
-      <c r="C70" t="str">
-        <v>الالتزام</v>
+        <v>تفقد البيئة المدرسية (9‏/4‏/1448هـ — 20‏/9‏/2026م)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>نظافة البيئة المدرسية</v>
+        <v>القسم</v>
       </c>
       <c r="B71" t="str">
-        <v>3/4</v>
+        <v>نعم/المجاب</v>
       </c>
       <c r="C71" t="str">
-        <v>75%</v>
+        <v>الالتزام</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>الفصول الدراسية</v>
+        <v>نظافة البيئة المدرسية</v>
       </c>
       <c r="B72" t="str">
-        <v>5/6</v>
+        <v>3/4</v>
       </c>
       <c r="C72" t="str">
-        <v>83%</v>
+        <v>75%</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>المياه</v>
+        <v>الفصول الدراسية</v>
       </c>
       <c r="B73" t="str">
-        <v>4/5</v>
+        <v>5/6</v>
       </c>
       <c r="C73" t="str">
-        <v>80%</v>
+        <v>83%</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>خدمات الصحة المدرسية</v>
+        <v>المياه</v>
       </c>
       <c r="B74" t="str">
-        <v>2/3</v>
+        <v>4/5</v>
       </c>
       <c r="C74" t="str">
-        <v>67%</v>
+        <v>80%</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
+        <v>خدمات الصحة المدرسية</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2/3</v>
+      </c>
+      <c r="C75" t="str">
+        <v>67%</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
         <v>المقصف المدرسي (وفق دليل الاشتراطات الصحية للمقاصف)</v>
       </c>
-      <c r="B75" t="str">
+      <c r="B76" t="str">
         <v>3/4</v>
       </c>
-      <c r="C75" t="str">
+      <c r="C76" t="str">
         <v>75%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H75"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H76"/>
   </ignoredErrors>
 </worksheet>
 </file>